--- a/output/pdf_financials_xlsx/CKG.xlsx
+++ b/output/pdf_financials_xlsx/CKG.xlsx
@@ -5951,46 +5951,46 @@
         <v>15.413068</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>17.4661</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>13.1542</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>14.9696</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>16.2076</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>19.1628</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>24.0169</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>25.1698</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>25.256</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>25.9272</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>28.45</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>28.076</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>31.799</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>28.954</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>32.029</v>
       </c>
     </row>
     <row r="93">
@@ -7438,16 +7438,16 @@
         <v>0</v>
       </c>
       <c r="O118" s="3" t="n">
-        <v>5.831</v>
+        <v>1.874</v>
       </c>
       <c r="P118" s="3" t="n">
-        <v>0.109</v>
+        <v>-3.909</v>
       </c>
       <c r="Q118" s="3" t="n">
-        <v>0</v>
+        <v>-6.634</v>
       </c>
       <c r="R118" s="3" t="n">
-        <v>0</v>
+        <v>-4.488</v>
       </c>
     </row>
     <row r="119">
@@ -10175,7 +10175,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>-</t>
@@ -13701,7 +13705,11 @@
           <t>Reserves 28,076</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr"/>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E54" t="inlineStr">
         <is>
           <t>-</t>
@@ -38309,7 +38317,11 @@
           <t>Exploration and evaluation expenditures 7</t>
         </is>
       </c>
-      <c r="D300" t="inlineStr"/>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E300" t="inlineStr">
         <is>
           <t>-</t>
@@ -40091,7 +40103,11 @@
           <t>(6,634)Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D318" t="inlineStr"/>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E318" t="inlineStr">
         <is>
           <t>-</t>
@@ -42164,7 +42180,11 @@
           <t>Exploration and evaluation expenditures 8</t>
         </is>
       </c>
-      <c r="D339" t="inlineStr"/>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E339" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/CKG.xlsx
+++ b/output/pdf_financials_xlsx/CKG.xlsx
@@ -2537,7 +2537,7 @@
         <v>15.6276</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>15.2582</v>
       </c>
       <c r="N34" s="3" t="n">
         <v>31.817</v>
@@ -2653,7 +2653,7 @@
         <v>16.9383</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>1.5445</v>
+        <v>16.8027</v>
       </c>
       <c r="N36" s="3" t="n">
         <v>32.153</v>
@@ -3349,7 +3349,7 @@
         <v>0.4404</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>15.808</v>
+        <v>0.5498</v>
       </c>
       <c r="N48" s="3" t="n">
         <v>0.8159999999999999</v>
@@ -7784,10 +7784,10 @@
         <v>0</v>
       </c>
       <c r="M124" s="3" t="n">
-        <v>0</v>
+        <v>-0.0069</v>
       </c>
       <c r="N124" s="3" t="n">
-        <v>0</v>
+        <v>-0.006</v>
       </c>
       <c r="O124" s="3" t="n">
         <v>0</v>
@@ -7842,10 +7842,10 @@
         <v>0</v>
       </c>
       <c r="M125" s="3" t="n">
-        <v>0</v>
+        <v>-0.0069</v>
       </c>
       <c r="N125" s="3" t="n">
-        <v>0</v>
+        <v>-0.006</v>
       </c>
       <c r="O125" s="3" t="n">
         <v>0</v>
@@ -9431,7 +9431,11 @@
           <t>Reclamation deposits</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>-</t>
@@ -14426,7 +14430,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -38216,7 +38220,11 @@
           <t>Reclamation deposit</t>
         </is>
       </c>
-      <c r="D299" t="inlineStr"/>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E299" t="inlineStr">
         <is>
           <t>-</t>
@@ -40002,7 +40010,11 @@
           <t>Reclamation deposit</t>
         </is>
       </c>
-      <c r="D317" t="inlineStr"/>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E317" t="inlineStr">
         <is>
           <t>-</t>
@@ -43976,7 +43988,11 @@
           <t>Lease payment</t>
         </is>
       </c>
-      <c r="D357" t="inlineStr"/>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E357" t="inlineStr">
         <is>
           <t>-</t>
@@ -44477,7 +44493,11 @@
           <t>Lease - payment</t>
         </is>
       </c>
-      <c r="D362" t="inlineStr"/>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E362" t="inlineStr">
         <is>
           <t>-</t>
@@ -46369,7 +46389,11 @@
           <t>Lease – payment</t>
         </is>
       </c>
-      <c r="D382" t="inlineStr"/>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E382" t="inlineStr">
         <is>
           <t>-</t>
